--- a/assets/downloads/excel-001-cost-calculator.xlsx
+++ b/assets/downloads/excel-001-cost-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/644b114873cb6133/Desktop/nijobair.github.io/assets/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{99E63637-56B4-4D77-BE28-D128DED63D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{631E0B7E-1263-4E61-A875-8BE2D78669D2}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{99E63637-56B4-4D77-BE28-D128DED63D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E5068A-70B3-4D6F-95FC-A6017EDBB7F3}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="665" activeTab="1" xr2:uid="{EC52426A-9AE1-4D31-A39F-90720DE78151}"/>
   </bookViews>
@@ -976,7 +976,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CB4A902C-1939-4C31-8352-8015C56418F3}" type="CELLRANGE">
+                    <a:fld id="{BA20E1BE-353A-44E7-BAA8-908EA989C1A7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1010,7 +1010,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8238DB89-721A-4F43-9713-ED3A3E764C7F}" type="CELLRANGE">
+                    <a:fld id="{A01084C6-7748-430E-A0E8-AEFC4C95BE10}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1099,7 +1099,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7641.9000000000005</c:v>
+                  <c:v>9170.2800000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8983.8000000000011</c:v>
@@ -1114,7 +1114,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="2"/>
                   <c:pt idx="0">
-                    <c:v>7.6K</c:v>
+                    <c:v>9.2K</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>9.0K</c:v>
@@ -1235,7 +1235,7 @@
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-1341.9000000000005</c:v>
+                    <c:v>186.47999999999956</c:v>
                   </c:pt>
                 </c:numCache>
               </c:numRef>
@@ -1336,7 +1336,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0DDA9FA4-28D7-4971-9C07-CB50399332D2}" type="CELLRANGE">
+                    <a:fld id="{3B8CAE9F-8AC5-44FE-B4E0-C89C3ADF0FBA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1427,7 +1427,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>8312.85</c:v>
+                  <c:v>9077.0400000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1440,7 +1440,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-1,342</c:v>
+                    <c:v>186</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -1717,7 +1717,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2EF76D6-F540-425E-A4DC-22E81ADA2255}" type="CELLRANGE">
+                    <a:fld id="{FC3A761F-D463-4BB7-B0CE-4077E8F583BF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1751,7 +1751,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{558E3E73-ABE7-48E1-936B-FACC4CF1C6AD}" type="CELLRANGE">
+                    <a:fld id="{5AE185AE-C259-4D34-AC28-780009BB7A5D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1840,7 +1840,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>32751</c:v>
+                  <c:v>39301.200000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>38502</c:v>
@@ -1855,7 +1855,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="2"/>
                   <c:pt idx="0">
-                    <c:v>32.8K</c:v>
+                    <c:v>39.3K</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>38.5K</c:v>
@@ -1962,7 +1962,7 @@
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-5751</c:v>
+                    <c:v>799.20000000000437</c:v>
                   </c:pt>
                 </c:numCache>
               </c:numRef>
@@ -2057,7 +2057,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5164FD06-5A91-4978-9FEA-4CC946F9BAEF}" type="CELLRANGE">
+                    <a:fld id="{1F2AB592-B492-4C34-AEA1-75C3F4547465}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2146,7 +2146,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>35626.5</c:v>
+                  <c:v>38901.600000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2159,7 +2159,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-5,751</c:v>
+                    <c:v>799</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -2435,7 +2435,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{95F49122-35AF-4460-ADDF-982E47AD16AD}" type="CELLRANGE">
+                    <a:fld id="{CE342E01-8E6B-4280-821F-E7CEACDE1255}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2469,7 +2469,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{42B428C6-0B99-4FCD-9F8A-78B98FD6962E}" type="CELLRANGE">
+                    <a:fld id="{AC1B5707-6690-4528-8A29-E9A2F5895E47}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2558,7 +2558,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>398470.5</c:v>
+                  <c:v>478164.60000000009</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>468441.00000000006</c:v>
@@ -2573,7 +2573,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="2"/>
                   <c:pt idx="0">
-                    <c:v>398.5K</c:v>
+                    <c:v>478.2K</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>468.4K</c:v>
@@ -2661,7 +2661,7 @@
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-69970.500000000058</c:v>
+                    <c:v>9723.6000000000349</c:v>
                   </c:pt>
                 </c:numCache>
               </c:numRef>
@@ -2756,7 +2756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{846D2C42-2CB1-42F3-9F98-315C3245F9B1}" type="CELLRANGE">
+                    <a:fld id="{D69ECDEB-AC9A-4022-9A73-AEAEC2AF18CC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2845,7 +2845,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>433455.75</c:v>
+                  <c:v>473302.80000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2858,7 +2858,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>-69,971</c:v>
+                    <c:v>9.7K</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -5748,7 +5748,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="25"/>
       <c r="G11" s="19"/>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B18" s="28">
         <f>( $B$10 * $B$11 ) * IF( $B$13 = "",$B$12,$B$13 ) * _xlfn.XLOOKUP( "Week", tblDays[Unit], tblDays[Day] )</f>
-        <v>7641.9000000000005</v>
+        <v>9170.2800000000007</v>
       </c>
       <c r="G18" s="19"/>
       <c r="H18" s="26" t="s">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="B19" s="28">
         <f>( $B$10 * $B$11 ) * IF( $B$13 = "",$B$12,$B$13 ) * _xlfn.XLOOKUP( "Month", tblDays[Unit], tblDays[Day] )</f>
-        <v>32751</v>
+        <v>39301.200000000004</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="26" t="s">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B20" s="28">
         <f>( $B$10 * $B$11 ) * IF( $B$13 = "",$B$12,$B$13 ) * _xlfn.XLOOKUP( "Year", tblDays[Unit], tblDays[Day] )</f>
-        <v>398470.5</v>
+        <v>478164.60000000009</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="26" t="s">
@@ -5948,7 +5948,7 @@
     <row r="42" x14ac:dyDescent="0.45"/>
     <row r="43" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B3+fNISNAgFi76olED48gO1hBMkP9T9xXZ53NNOC4IZb000Sm+2X7RNTHtPCoI5bRwd4HM6PioV/RjqnHg+2fw==" saltValue="+JdjmOwAtU7g0j+hJ6BEHQ==" spinCount="100000" sheet="1" objects="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{EBA900FE-7B8E-4219-A90A-061259A370E9}">
       <formula1>rngStates</formula1>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="Y4" s="34" cm="1">
         <f t="array" ref="Y4:Y6">Calculator!$B$18:$B$20</f>
-        <v>7641.9000000000005</v>
+        <v>9170.2800000000007</v>
       </c>
       <c r="Z4" s="34" cm="1">
         <f t="array" ref="Z4:Z6">Calculator!I18:I20</f>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AA4" s="34" t="str">
         <f>IF(Y4&gt;999,TEXT(Y4,"#,#0,.0K"),TEXT(Y4,"#,#"))</f>
-        <v>7.6K</v>
+        <v>9.2K</v>
       </c>
       <c r="AB4" s="34" t="str">
         <f>IF(Z4&gt;999,TEXT(Z4,"#,#0,.0K"),TEXT(Z4,"#,#"))</f>
@@ -6192,15 +6192,15 @@
       </c>
       <c r="AD4" s="34">
         <f>Y4-Z4</f>
-        <v>-1341.9000000000005</v>
+        <v>186.47999999999956</v>
       </c>
       <c r="AE4" s="34" t="str">
         <f>IF(AD4&gt;999,TEXT(AD4,"#,#0,.0K"),TEXT(AD4,"#,#"))</f>
-        <v>-1,342</v>
+        <v>186</v>
       </c>
       <c r="AF4" s="34">
         <f>AVERAGE(Y4:Z4)</f>
-        <v>8312.85</v>
+        <v>9077.0400000000009</v>
       </c>
       <c r="AG4" s="34"/>
     </row>
@@ -6235,14 +6235,14 @@
         <v>32</v>
       </c>
       <c r="Y5" s="34">
-        <v>32751</v>
+        <v>39301.200000000004</v>
       </c>
       <c r="Z5" s="34">
         <v>38502</v>
       </c>
       <c r="AA5" s="34" t="str">
         <f>IF(Y5&gt;999,TEXT(Y5,"#,#0,.0K"),TEXT(Y5,"#,#"))</f>
-        <v>32.8K</v>
+        <v>39.3K</v>
       </c>
       <c r="AB5" s="34" t="str">
         <f t="shared" ref="AB5:AB6" si="0">IF(Z5&gt;999,TEXT(Z5,"#,#0,.0K"),TEXT(Z5,"#,#"))</f>
@@ -6253,15 +6253,15 @@
       </c>
       <c r="AD5" s="34">
         <f t="shared" ref="AD5:AD6" si="1">Y5-Z5</f>
-        <v>-5751</v>
+        <v>799.20000000000437</v>
       </c>
       <c r="AE5" s="34" t="str">
         <f t="shared" ref="AE5:AE6" si="2">IF(AD5&gt;999,TEXT(AD5,"#,#0,.0K"),TEXT(AD5,"#,#"))</f>
-        <v>-5,751</v>
+        <v>799</v>
       </c>
       <c r="AF5" s="34">
         <f t="shared" ref="AF5:AF6" si="3">AVERAGE(Y5:Z5)</f>
-        <v>35626.5</v>
+        <v>38901.600000000006</v>
       </c>
       <c r="AG5" s="34"/>
     </row>
@@ -6298,14 +6298,14 @@
         <v>33</v>
       </c>
       <c r="Y6" s="34">
-        <v>398470.5</v>
+        <v>478164.60000000009</v>
       </c>
       <c r="Z6" s="34">
         <v>468441.00000000006</v>
       </c>
       <c r="AA6" s="34" t="str">
         <f>IF(Y6&gt;999,TEXT(Y6,"#,#0,.0K"),TEXT(Y6,"#,#"))</f>
-        <v>398.5K</v>
+        <v>478.2K</v>
       </c>
       <c r="AB6" s="34" t="str">
         <f t="shared" si="0"/>
@@ -6316,15 +6316,15 @@
       </c>
       <c r="AD6" s="34">
         <f t="shared" si="1"/>
-        <v>-69970.500000000058</v>
+        <v>9723.6000000000349</v>
       </c>
       <c r="AE6" s="34" t="str">
         <f t="shared" si="2"/>
-        <v>-69,971</v>
+        <v>9.7K</v>
       </c>
       <c r="AF6" s="34">
         <f t="shared" si="3"/>
-        <v>433455.75</v>
+        <v>473302.80000000005</v>
       </c>
       <c r="AG6" s="34"/>
     </row>
